--- a/UTAIR_EXP_Frequent_RFQ_v2.xlsx
+++ b/UTAIR_EXP_Frequent_RFQ_v2.xlsx
@@ -20,8 +20,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="#,##0.##"/>
+    <numFmt numFmtId="165" formatCode="0.##"/>
   </numFmts>
   <fonts count="3">
     <font>
@@ -92,7 +93,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -129,6 +130,12 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -689,7 +696,7 @@
       <c r="D2" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="E2" s="6" t="n">
+      <c r="E2" s="14" t="n">
         <v>67</v>
       </c>
       <c r="F2" s="3" t="n">
@@ -718,7 +725,7 @@
       <c r="D3" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="E3" s="12" t="n">
+      <c r="E3" s="15" t="n">
         <v>18</v>
       </c>
       <c r="F3" s="9" t="n">
@@ -747,7 +754,7 @@
       <c r="D4" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="E4" s="6" t="n">
+      <c r="E4" s="14" t="n">
         <v>288</v>
       </c>
       <c r="F4" s="3" t="n">
@@ -776,7 +783,7 @@
       <c r="D5" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="E5" s="12" t="n">
+      <c r="E5" s="15" t="n">
         <v>6</v>
       </c>
       <c r="F5" s="9" t="n">
@@ -805,7 +812,7 @@
       <c r="D6" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="E6" s="6" t="n">
+      <c r="E6" s="14" t="n">
         <v>1360</v>
       </c>
       <c r="F6" s="3" t="n">
@@ -834,7 +841,7 @@
       <c r="D7" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="E7" s="12" t="n">
+      <c r="E7" s="15" t="n">
         <v>48</v>
       </c>
       <c r="F7" s="9" t="n">
@@ -863,7 +870,7 @@
       <c r="D8" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="E8" s="6" t="n">
+      <c r="E8" s="14" t="n">
         <v>7</v>
       </c>
       <c r="F8" s="3" t="n">
@@ -892,7 +899,7 @@
       <c r="D9" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="E9" s="12" t="n">
+      <c r="E9" s="15" t="n">
         <v>17</v>
       </c>
       <c r="F9" s="9" t="n">
@@ -921,7 +928,7 @@
       <c r="D10" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="E10" s="6" t="n">
+      <c r="E10" s="14" t="n">
         <v>9</v>
       </c>
       <c r="F10" s="3" t="n">
@@ -950,7 +957,7 @@
       <c r="D11" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="E11" s="12" t="n">
+      <c r="E11" s="15" t="n">
         <v>6</v>
       </c>
       <c r="F11" s="9" t="n">
@@ -979,7 +986,7 @@
       <c r="D12" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="E12" s="6" t="n">
+      <c r="E12" s="14" t="n">
         <v>25</v>
       </c>
       <c r="F12" s="3" t="n">
@@ -1008,7 +1015,7 @@
       <c r="D13" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="E13" s="12" t="n">
+      <c r="E13" s="15" t="n">
         <v>6</v>
       </c>
       <c r="F13" s="9" t="n">
@@ -1037,7 +1044,7 @@
       <c r="D14" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="E14" s="6" t="n">
+      <c r="E14" s="14" t="n">
         <v>17</v>
       </c>
       <c r="F14" s="3" t="n">
@@ -1066,7 +1073,7 @@
       <c r="D15" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="E15" s="12" t="n">
+      <c r="E15" s="15" t="n">
         <v>38</v>
       </c>
       <c r="F15" s="9" t="n">
@@ -1095,7 +1102,7 @@
       <c r="D16" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="E16" s="6" t="n">
+      <c r="E16" s="14" t="n">
         <v>120</v>
       </c>
       <c r="F16" s="3" t="n">
@@ -1124,7 +1131,7 @@
       <c r="D17" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="E17" s="12" t="n">
+      <c r="E17" s="15" t="n">
         <v>4</v>
       </c>
       <c r="F17" s="9" t="n">
@@ -1153,7 +1160,7 @@
       <c r="D18" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="E18" s="6" t="n">
+      <c r="E18" s="14" t="n">
         <v>14</v>
       </c>
       <c r="F18" s="3" t="n">
@@ -1182,7 +1189,7 @@
       <c r="D19" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="E19" s="12" t="n">
+      <c r="E19" s="15" t="n">
         <v>21</v>
       </c>
       <c r="F19" s="9" t="n">
@@ -1211,7 +1218,7 @@
       <c r="D20" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="E20" s="6" t="n">
+      <c r="E20" s="14" t="n">
         <v>105</v>
       </c>
       <c r="F20" s="3" t="n">
@@ -1240,7 +1247,7 @@
       <c r="D21" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="E21" s="12" t="n">
+      <c r="E21" s="15" t="n">
         <v>35</v>
       </c>
       <c r="F21" s="9" t="n">
@@ -1269,7 +1276,7 @@
       <c r="D22" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="E22" s="6" t="n">
+      <c r="E22" s="14" t="n">
         <v>690</v>
       </c>
       <c r="F22" s="3" t="n">
@@ -1298,7 +1305,7 @@
       <c r="D23" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="E23" s="12" t="n">
+      <c r="E23" s="15" t="n">
         <v>26</v>
       </c>
       <c r="F23" s="9" t="n">
@@ -1327,7 +1334,7 @@
       <c r="D24" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="E24" s="6" t="n">
+      <c r="E24" s="14" t="n">
         <v>3122</v>
       </c>
       <c r="F24" s="3" t="n">
@@ -1356,7 +1363,7 @@
       <c r="D25" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="E25" s="12" t="n">
+      <c r="E25" s="15" t="n">
         <v>224</v>
       </c>
       <c r="F25" s="9" t="n">
@@ -1385,7 +1392,7 @@
       <c r="D26" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="E26" s="6" t="n">
+      <c r="E26" s="14" t="n">
         <v>20</v>
       </c>
       <c r="F26" s="3" t="n">

--- a/UTAIR_EXP_Frequent_RFQ_v2.xlsx
+++ b/UTAIR_EXP_Frequent_RFQ_v2.xlsx
@@ -20,10 +20,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="#,##0.##"/>
-    <numFmt numFmtId="165" formatCode="0.##"/>
-  </numFmts>
+  <numFmts count="0"/>
   <fonts count="3">
     <font>
       <name val="Calibri"/>
@@ -93,7 +90,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -108,7 +105,7 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="1" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="4" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -126,16 +123,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -504,9 +495,9 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:A17"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
-    <col width="100" customWidth="1" min="1" max="1"/>
+    <col width="110" customWidth="1" min="1" max="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -575,14 +566,14 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Our offers count — number of commercial offers we provided</t>
+          <t>Our offers count — number of commercial offers we sent (1 per RFQ; options calculated for comparison are not counted separately)</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Our average offer price EA (USD) — average unit price in our offers (DDP MOW basis)</t>
+          <t>Our average offer price EA (USD) — average unit price of sent offers (DDP MOW basis)</t>
         </is>
       </c>
     </row>
@@ -619,7 +610,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:I26"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
     <col width="20" customWidth="1" min="2" max="2"/>
@@ -696,7 +687,7 @@
       <c r="D2" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="E2" s="14" t="n">
+      <c r="E2" s="6" t="n">
         <v>67</v>
       </c>
       <c r="F2" s="3" t="n">
@@ -725,7 +716,7 @@
       <c r="D3" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="E3" s="15" t="n">
+      <c r="E3" s="12" t="n">
         <v>18</v>
       </c>
       <c r="F3" s="9" t="n">
@@ -754,7 +745,7 @@
       <c r="D4" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="E4" s="14" t="n">
+      <c r="E4" s="6" t="n">
         <v>288</v>
       </c>
       <c r="F4" s="3" t="n">
@@ -783,7 +774,7 @@
       <c r="D5" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="E5" s="15" t="n">
+      <c r="E5" s="12" t="n">
         <v>6</v>
       </c>
       <c r="F5" s="9" t="n">
@@ -812,7 +803,7 @@
       <c r="D6" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="E6" s="14" t="n">
+      <c r="E6" s="6" t="n">
         <v>1360</v>
       </c>
       <c r="F6" s="3" t="n">
@@ -841,14 +832,14 @@
       <c r="D7" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="E7" s="15" t="n">
+      <c r="E7" s="12" t="n">
         <v>48</v>
       </c>
       <c r="F7" s="9" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="G7" s="13" t="n">
-        <v>1425.71</v>
+        <v>2146.67</v>
       </c>
       <c r="H7" s="8" t="inlineStr"/>
       <c r="I7" s="8" t="inlineStr"/>
@@ -870,7 +861,7 @@
       <c r="D8" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="E8" s="14" t="n">
+      <c r="E8" s="6" t="n">
         <v>7</v>
       </c>
       <c r="F8" s="3" t="n">
@@ -899,7 +890,7 @@
       <c r="D9" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="E9" s="15" t="n">
+      <c r="E9" s="12" t="n">
         <v>17</v>
       </c>
       <c r="F9" s="9" t="n">
@@ -928,7 +919,7 @@
       <c r="D10" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="E10" s="14" t="n">
+      <c r="E10" s="6" t="n">
         <v>9</v>
       </c>
       <c r="F10" s="3" t="n">
@@ -957,7 +948,7 @@
       <c r="D11" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="E11" s="15" t="n">
+      <c r="E11" s="12" t="n">
         <v>6</v>
       </c>
       <c r="F11" s="9" t="n">
@@ -986,11 +977,11 @@
       <c r="D12" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="E12" s="14" t="n">
+      <c r="E12" s="6" t="n">
         <v>25</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G12" s="7" t="n">
         <v>7005</v>
@@ -1015,7 +1006,7 @@
       <c r="D13" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="E13" s="15" t="n">
+      <c r="E13" s="12" t="n">
         <v>6</v>
       </c>
       <c r="F13" s="9" t="n">
@@ -1044,11 +1035,11 @@
       <c r="D14" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="E14" s="14" t="n">
+      <c r="E14" s="6" t="n">
         <v>17</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G14" s="7" t="n">
         <v>4130</v>
@@ -1073,7 +1064,7 @@
       <c r="D15" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="E15" s="15" t="n">
+      <c r="E15" s="12" t="n">
         <v>38</v>
       </c>
       <c r="F15" s="9" t="n">
@@ -1102,7 +1093,7 @@
       <c r="D16" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="E16" s="14" t="n">
+      <c r="E16" s="6" t="n">
         <v>120</v>
       </c>
       <c r="F16" s="3" t="n">
@@ -1131,7 +1122,7 @@
       <c r="D17" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="E17" s="15" t="n">
+      <c r="E17" s="12" t="n">
         <v>4</v>
       </c>
       <c r="F17" s="9" t="n">
@@ -1160,7 +1151,7 @@
       <c r="D18" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="E18" s="14" t="n">
+      <c r="E18" s="6" t="n">
         <v>14</v>
       </c>
       <c r="F18" s="3" t="n">
@@ -1189,7 +1180,7 @@
       <c r="D19" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="E19" s="15" t="n">
+      <c r="E19" s="12" t="n">
         <v>21</v>
       </c>
       <c r="F19" s="9" t="n">
@@ -1218,11 +1209,11 @@
       <c r="D20" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="E20" s="14" t="n">
+      <c r="E20" s="6" t="n">
         <v>105</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G20" s="7" t="n">
         <v>295</v>
@@ -1247,7 +1238,7 @@
       <c r="D21" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="E21" s="15" t="n">
+      <c r="E21" s="12" t="n">
         <v>35</v>
       </c>
       <c r="F21" s="9" t="n">
@@ -1276,7 +1267,7 @@
       <c r="D22" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="E22" s="14" t="n">
+      <c r="E22" s="6" t="n">
         <v>690</v>
       </c>
       <c r="F22" s="3" t="n">
@@ -1305,7 +1296,7 @@
       <c r="D23" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="E23" s="15" t="n">
+      <c r="E23" s="12" t="n">
         <v>26</v>
       </c>
       <c r="F23" s="9" t="n">
@@ -1334,7 +1325,7 @@
       <c r="D24" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="E24" s="14" t="n">
+      <c r="E24" s="6" t="n">
         <v>3122</v>
       </c>
       <c r="F24" s="3" t="n">
@@ -1363,7 +1354,7 @@
       <c r="D25" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="E25" s="15" t="n">
+      <c r="E25" s="12" t="n">
         <v>224</v>
       </c>
       <c r="F25" s="9" t="n">
@@ -1392,7 +1383,7 @@
       <c r="D26" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="E26" s="14" t="n">
+      <c r="E26" s="6" t="n">
         <v>20</v>
       </c>
       <c r="F26" s="3" t="n">
@@ -1417,9 +1408,9 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:A17"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
-    <col width="100" customWidth="1" min="1" max="1"/>
+    <col width="110" customWidth="1" min="1" max="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1488,14 +1479,14 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Our offers count — сколько коммерческих предложений мы направили</t>
+          <t>Our offers count — число отправленных предложений (1 на RFQ; варианты «для сравнения» отдельно не считаются)</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Our average offer price EA (USD) — средняя цена за единицу в наших предложениях (база DDP MOW)</t>
+          <t>Our average offer price EA (USD) — средняя цена за единицу в отправленных предложениях (база DDP MOW)</t>
         </is>
       </c>
     </row>
